--- a/AAII_Financials/Quarterly/VWFB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VWFB_QTR_FIN.xlsx
@@ -1754,7 +1754,7 @@
         <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="3">
         <v>1000</v>
